--- a/Workout-Templates.xlsx
+++ b/Workout-Templates.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/n1k0/Projects/Workout-Tracker/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C7D8D675-69C2-484B-B045-D9DEF0DCCB6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDF83B94-ED0C-F54C-BF62-0BB9DBA0A1EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{4CE66275-5C1E-1444-9166-C36D08002208}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="437" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="793" uniqueCount="63">
   <si>
     <t>WorkoutID</t>
   </si>
@@ -171,6 +171,60 @@
   </si>
   <si>
     <t>Wadenheben Beinpresse</t>
+  </si>
+  <si>
+    <t>Upper Low Voume A</t>
+  </si>
+  <si>
+    <t>Schräg Kurzhantel Y-Raise</t>
+  </si>
+  <si>
+    <t>Kelso Shrug</t>
+  </si>
+  <si>
+    <t>EZ-Bar Preacher Curl</t>
+  </si>
+  <si>
+    <t>Kabel Bar Trizeps Pushdown</t>
+  </si>
+  <si>
+    <t>Lower Low Voume A</t>
+  </si>
+  <si>
+    <t>Smith Maschine Lunge</t>
+  </si>
+  <si>
+    <t>Wadenpresse sitzend</t>
+  </si>
+  <si>
+    <t>Upper Low Voume B</t>
+  </si>
+  <si>
+    <t>Maschine Rudern breiter Griff</t>
+  </si>
+  <si>
+    <t>Brustpresse</t>
+  </si>
+  <si>
+    <t>Unilateral Butterfly Reverse</t>
+  </si>
+  <si>
+    <t>Lower Low Voume B</t>
+  </si>
+  <si>
+    <t>Hip Thrust</t>
+  </si>
+  <si>
+    <t>Arms and Delts Low Voume</t>
+  </si>
+  <si>
+    <t>Zotman Curl</t>
+  </si>
+  <si>
+    <t>Kurzhantel Bizeps Curl</t>
+  </si>
+  <si>
+    <t>Maschine Seitheben</t>
   </si>
 </sst>
 </file>
@@ -550,10 +604,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5254F6D-4319-9C4D-A83B-05D87FCC2785}">
-  <dimension ref="A1:I108"/>
+  <dimension ref="A1:I197"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="12.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.83203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="31.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3689,6 +3743,2587 @@
         <v>0</v>
       </c>
     </row>
+    <row r="109" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A109">
+        <v>6</v>
+      </c>
+      <c r="B109" t="s">
+        <v>45</v>
+      </c>
+      <c r="C109">
+        <v>55</v>
+      </c>
+      <c r="D109" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E109" t="s">
+        <v>11</v>
+      </c>
+      <c r="F109" t="s">
+        <v>12</v>
+      </c>
+      <c r="G109">
+        <v>10</v>
+      </c>
+      <c r="H109">
+        <v>30</v>
+      </c>
+      <c r="I109">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A110">
+        <v>6</v>
+      </c>
+      <c r="B110" t="s">
+        <v>45</v>
+      </c>
+      <c r="C110">
+        <v>55</v>
+      </c>
+      <c r="D110" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E110" t="s">
+        <v>11</v>
+      </c>
+      <c r="F110" t="s">
+        <v>12</v>
+      </c>
+      <c r="G110">
+        <v>6</v>
+      </c>
+      <c r="H110">
+        <v>50</v>
+      </c>
+      <c r="I110">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A111">
+        <v>6</v>
+      </c>
+      <c r="B111" t="s">
+        <v>45</v>
+      </c>
+      <c r="C111">
+        <v>55</v>
+      </c>
+      <c r="D111" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E111" t="s">
+        <v>12</v>
+      </c>
+      <c r="F111" t="s">
+        <v>11</v>
+      </c>
+      <c r="G111">
+        <v>6</v>
+      </c>
+      <c r="H111">
+        <v>70</v>
+      </c>
+      <c r="I111">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A112">
+        <v>6</v>
+      </c>
+      <c r="B112" t="s">
+        <v>45</v>
+      </c>
+      <c r="C112">
+        <v>55</v>
+      </c>
+      <c r="D112" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E112" t="s">
+        <v>12</v>
+      </c>
+      <c r="F112" t="s">
+        <v>11</v>
+      </c>
+      <c r="G112">
+        <v>6</v>
+      </c>
+      <c r="H112">
+        <v>70</v>
+      </c>
+      <c r="I112">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A113">
+        <v>6</v>
+      </c>
+      <c r="B113" t="s">
+        <v>45</v>
+      </c>
+      <c r="C113">
+        <v>56</v>
+      </c>
+      <c r="D113" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E113" t="s">
+        <v>11</v>
+      </c>
+      <c r="F113" t="s">
+        <v>12</v>
+      </c>
+      <c r="G113">
+        <v>10</v>
+      </c>
+      <c r="H113">
+        <v>60</v>
+      </c>
+      <c r="I113">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A114">
+        <v>6</v>
+      </c>
+      <c r="B114" t="s">
+        <v>45</v>
+      </c>
+      <c r="C114">
+        <v>56</v>
+      </c>
+      <c r="D114" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E114" t="s">
+        <v>12</v>
+      </c>
+      <c r="F114" t="s">
+        <v>11</v>
+      </c>
+      <c r="G114">
+        <v>10</v>
+      </c>
+      <c r="H114">
+        <v>105</v>
+      </c>
+      <c r="I114">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A115">
+        <v>6</v>
+      </c>
+      <c r="B115" t="s">
+        <v>45</v>
+      </c>
+      <c r="C115">
+        <v>56</v>
+      </c>
+      <c r="D115" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E115" t="s">
+        <v>12</v>
+      </c>
+      <c r="F115" t="s">
+        <v>11</v>
+      </c>
+      <c r="G115">
+        <v>10</v>
+      </c>
+      <c r="H115">
+        <v>105</v>
+      </c>
+      <c r="I115">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A116">
+        <v>6</v>
+      </c>
+      <c r="B116" t="s">
+        <v>45</v>
+      </c>
+      <c r="C116">
+        <v>103</v>
+      </c>
+      <c r="D116" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E116" t="s">
+        <v>11</v>
+      </c>
+      <c r="F116" t="s">
+        <v>12</v>
+      </c>
+      <c r="G116">
+        <v>10</v>
+      </c>
+      <c r="H116">
+        <v>6</v>
+      </c>
+      <c r="I116">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A117">
+        <v>6</v>
+      </c>
+      <c r="B117" t="s">
+        <v>45</v>
+      </c>
+      <c r="C117">
+        <v>103</v>
+      </c>
+      <c r="D117" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E117" t="s">
+        <v>12</v>
+      </c>
+      <c r="F117" t="s">
+        <v>11</v>
+      </c>
+      <c r="G117">
+        <v>10</v>
+      </c>
+      <c r="H117">
+        <v>12</v>
+      </c>
+      <c r="I117">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A118">
+        <v>6</v>
+      </c>
+      <c r="B118" t="s">
+        <v>45</v>
+      </c>
+      <c r="C118">
+        <v>103</v>
+      </c>
+      <c r="D118" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E118" t="s">
+        <v>12</v>
+      </c>
+      <c r="F118" t="s">
+        <v>11</v>
+      </c>
+      <c r="G118">
+        <v>10</v>
+      </c>
+      <c r="H118">
+        <v>12</v>
+      </c>
+      <c r="I118">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A119">
+        <v>6</v>
+      </c>
+      <c r="B119" t="s">
+        <v>45</v>
+      </c>
+      <c r="C119">
+        <v>5</v>
+      </c>
+      <c r="D119" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E119" t="s">
+        <v>11</v>
+      </c>
+      <c r="F119" t="s">
+        <v>12</v>
+      </c>
+      <c r="G119">
+        <v>10</v>
+      </c>
+      <c r="H119">
+        <v>25</v>
+      </c>
+      <c r="I119">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A120">
+        <v>6</v>
+      </c>
+      <c r="B120" t="s">
+        <v>45</v>
+      </c>
+      <c r="C120">
+        <v>5</v>
+      </c>
+      <c r="D120" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E120" t="s">
+        <v>11</v>
+      </c>
+      <c r="F120" t="s">
+        <v>12</v>
+      </c>
+      <c r="G120">
+        <v>6</v>
+      </c>
+      <c r="H120">
+        <v>40</v>
+      </c>
+      <c r="I120">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A121">
+        <v>6</v>
+      </c>
+      <c r="B121" t="s">
+        <v>45</v>
+      </c>
+      <c r="C121">
+        <v>5</v>
+      </c>
+      <c r="D121" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E121" t="s">
+        <v>12</v>
+      </c>
+      <c r="F121" t="s">
+        <v>11</v>
+      </c>
+      <c r="G121">
+        <v>8</v>
+      </c>
+      <c r="H121">
+        <v>50</v>
+      </c>
+      <c r="I121">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A122">
+        <v>6</v>
+      </c>
+      <c r="B122" t="s">
+        <v>45</v>
+      </c>
+      <c r="C122">
+        <v>5</v>
+      </c>
+      <c r="D122" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E122" t="s">
+        <v>12</v>
+      </c>
+      <c r="F122" t="s">
+        <v>11</v>
+      </c>
+      <c r="G122">
+        <v>8</v>
+      </c>
+      <c r="H122">
+        <v>50</v>
+      </c>
+      <c r="I122">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A123">
+        <v>6</v>
+      </c>
+      <c r="B123" t="s">
+        <v>45</v>
+      </c>
+      <c r="C123">
+        <v>31</v>
+      </c>
+      <c r="D123" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E123" t="s">
+        <v>11</v>
+      </c>
+      <c r="F123" t="s">
+        <v>12</v>
+      </c>
+      <c r="G123">
+        <v>10</v>
+      </c>
+      <c r="H123">
+        <v>70</v>
+      </c>
+      <c r="I123">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A124">
+        <v>6</v>
+      </c>
+      <c r="B124" t="s">
+        <v>45</v>
+      </c>
+      <c r="C124">
+        <v>31</v>
+      </c>
+      <c r="D124" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E124" t="s">
+        <v>12</v>
+      </c>
+      <c r="F124" t="s">
+        <v>11</v>
+      </c>
+      <c r="G124">
+        <v>10</v>
+      </c>
+      <c r="H124">
+        <v>130</v>
+      </c>
+      <c r="I124">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A125">
+        <v>6</v>
+      </c>
+      <c r="B125" t="s">
+        <v>45</v>
+      </c>
+      <c r="C125">
+        <v>31</v>
+      </c>
+      <c r="D125" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E125" t="s">
+        <v>12</v>
+      </c>
+      <c r="F125" t="s">
+        <v>11</v>
+      </c>
+      <c r="G125">
+        <v>10</v>
+      </c>
+      <c r="H125">
+        <v>130</v>
+      </c>
+      <c r="I125">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A126">
+        <v>6</v>
+      </c>
+      <c r="B126" t="s">
+        <v>45</v>
+      </c>
+      <c r="C126">
+        <v>47</v>
+      </c>
+      <c r="D126" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E126" t="s">
+        <v>11</v>
+      </c>
+      <c r="F126" t="s">
+        <v>12</v>
+      </c>
+      <c r="G126">
+        <v>10</v>
+      </c>
+      <c r="H126">
+        <v>10</v>
+      </c>
+      <c r="I126">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A127">
+        <v>6</v>
+      </c>
+      <c r="B127" t="s">
+        <v>45</v>
+      </c>
+      <c r="C127">
+        <v>47</v>
+      </c>
+      <c r="D127" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E127" t="s">
+        <v>12</v>
+      </c>
+      <c r="F127" t="s">
+        <v>11</v>
+      </c>
+      <c r="G127">
+        <v>10</v>
+      </c>
+      <c r="H127">
+        <v>20</v>
+      </c>
+      <c r="I127">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A128">
+        <v>6</v>
+      </c>
+      <c r="B128" t="s">
+        <v>45</v>
+      </c>
+      <c r="C128">
+        <v>47</v>
+      </c>
+      <c r="D128" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E128" t="s">
+        <v>12</v>
+      </c>
+      <c r="F128" t="s">
+        <v>11</v>
+      </c>
+      <c r="G128">
+        <v>10</v>
+      </c>
+      <c r="H128">
+        <v>20</v>
+      </c>
+      <c r="I128">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A129">
+        <v>6</v>
+      </c>
+      <c r="B129" t="s">
+        <v>45</v>
+      </c>
+      <c r="C129">
+        <v>106</v>
+      </c>
+      <c r="D129" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E129" t="s">
+        <v>11</v>
+      </c>
+      <c r="F129" t="s">
+        <v>12</v>
+      </c>
+      <c r="G129">
+        <v>10</v>
+      </c>
+      <c r="H129">
+        <v>20</v>
+      </c>
+      <c r="I129">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A130">
+        <v>6</v>
+      </c>
+      <c r="B130" t="s">
+        <v>45</v>
+      </c>
+      <c r="C130">
+        <v>106</v>
+      </c>
+      <c r="D130" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E130" t="s">
+        <v>12</v>
+      </c>
+      <c r="F130" t="s">
+        <v>11</v>
+      </c>
+      <c r="G130">
+        <v>10</v>
+      </c>
+      <c r="H130">
+        <v>36</v>
+      </c>
+      <c r="I130">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A131">
+        <v>6</v>
+      </c>
+      <c r="B131" t="s">
+        <v>45</v>
+      </c>
+      <c r="C131">
+        <v>106</v>
+      </c>
+      <c r="D131" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E131" t="s">
+        <v>12</v>
+      </c>
+      <c r="F131" t="s">
+        <v>11</v>
+      </c>
+      <c r="G131">
+        <v>10</v>
+      </c>
+      <c r="H131">
+        <v>36</v>
+      </c>
+      <c r="I131">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A132">
+        <v>7</v>
+      </c>
+      <c r="B132" t="s">
+        <v>50</v>
+      </c>
+      <c r="C132">
+        <v>63</v>
+      </c>
+      <c r="D132" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E132" t="s">
+        <v>11</v>
+      </c>
+      <c r="F132" t="s">
+        <v>12</v>
+      </c>
+      <c r="G132">
+        <v>10</v>
+      </c>
+      <c r="H132">
+        <v>60</v>
+      </c>
+      <c r="I132">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A133">
+        <v>7</v>
+      </c>
+      <c r="B133" t="s">
+        <v>50</v>
+      </c>
+      <c r="C133">
+        <v>63</v>
+      </c>
+      <c r="D133" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E133" t="s">
+        <v>12</v>
+      </c>
+      <c r="F133" t="s">
+        <v>11</v>
+      </c>
+      <c r="G133">
+        <v>10</v>
+      </c>
+      <c r="H133">
+        <v>85</v>
+      </c>
+      <c r="I133">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A134">
+        <v>7</v>
+      </c>
+      <c r="B134" t="s">
+        <v>50</v>
+      </c>
+      <c r="C134">
+        <v>63</v>
+      </c>
+      <c r="D134" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E134" t="s">
+        <v>12</v>
+      </c>
+      <c r="F134" t="s">
+        <v>11</v>
+      </c>
+      <c r="G134">
+        <v>10</v>
+      </c>
+      <c r="H134">
+        <v>85</v>
+      </c>
+      <c r="I134">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A135">
+        <v>7</v>
+      </c>
+      <c r="B135" t="s">
+        <v>50</v>
+      </c>
+      <c r="C135">
+        <v>83</v>
+      </c>
+      <c r="D135" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E135" t="s">
+        <v>11</v>
+      </c>
+      <c r="F135" t="s">
+        <v>12</v>
+      </c>
+      <c r="G135">
+        <v>10</v>
+      </c>
+      <c r="H135">
+        <v>30</v>
+      </c>
+      <c r="I135">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A136">
+        <v>7</v>
+      </c>
+      <c r="B136" t="s">
+        <v>50</v>
+      </c>
+      <c r="C136">
+        <v>83</v>
+      </c>
+      <c r="D136" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E136" t="s">
+        <v>11</v>
+      </c>
+      <c r="F136" t="s">
+        <v>12</v>
+      </c>
+      <c r="G136">
+        <v>6</v>
+      </c>
+      <c r="H136">
+        <v>60</v>
+      </c>
+      <c r="I136">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A137">
+        <v>7</v>
+      </c>
+      <c r="B137" t="s">
+        <v>50</v>
+      </c>
+      <c r="C137">
+        <v>83</v>
+      </c>
+      <c r="D137" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E137" t="s">
+        <v>12</v>
+      </c>
+      <c r="F137" t="s">
+        <v>11</v>
+      </c>
+      <c r="G137">
+        <v>10</v>
+      </c>
+      <c r="H137">
+        <v>90</v>
+      </c>
+      <c r="I137">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A138">
+        <v>7</v>
+      </c>
+      <c r="B138" t="s">
+        <v>50</v>
+      </c>
+      <c r="C138">
+        <v>83</v>
+      </c>
+      <c r="D138" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E138" t="s">
+        <v>12</v>
+      </c>
+      <c r="F138" t="s">
+        <v>11</v>
+      </c>
+      <c r="G138">
+        <v>10</v>
+      </c>
+      <c r="H138">
+        <v>90</v>
+      </c>
+      <c r="I138">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A139">
+        <v>7</v>
+      </c>
+      <c r="B139" t="s">
+        <v>50</v>
+      </c>
+      <c r="C139">
+        <v>75</v>
+      </c>
+      <c r="D139" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E139" t="s">
+        <v>11</v>
+      </c>
+      <c r="F139" t="s">
+        <v>12</v>
+      </c>
+      <c r="G139">
+        <v>10</v>
+      </c>
+      <c r="H139">
+        <v>10</v>
+      </c>
+      <c r="I139">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A140">
+        <v>7</v>
+      </c>
+      <c r="B140" t="s">
+        <v>50</v>
+      </c>
+      <c r="C140">
+        <v>75</v>
+      </c>
+      <c r="D140" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E140" t="s">
+        <v>12</v>
+      </c>
+      <c r="F140" t="s">
+        <v>11</v>
+      </c>
+      <c r="G140">
+        <v>10</v>
+      </c>
+      <c r="H140">
+        <v>20</v>
+      </c>
+      <c r="I140">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A141">
+        <v>7</v>
+      </c>
+      <c r="B141" t="s">
+        <v>50</v>
+      </c>
+      <c r="C141">
+        <v>84</v>
+      </c>
+      <c r="D141" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E141" t="s">
+        <v>11</v>
+      </c>
+      <c r="F141" t="s">
+        <v>12</v>
+      </c>
+      <c r="G141">
+        <v>10</v>
+      </c>
+      <c r="H141">
+        <v>75</v>
+      </c>
+      <c r="I141">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A142">
+        <v>7</v>
+      </c>
+      <c r="B142" t="s">
+        <v>50</v>
+      </c>
+      <c r="C142">
+        <v>84</v>
+      </c>
+      <c r="D142" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E142" t="s">
+        <v>12</v>
+      </c>
+      <c r="F142" t="s">
+        <v>11</v>
+      </c>
+      <c r="G142">
+        <v>10</v>
+      </c>
+      <c r="H142">
+        <v>115</v>
+      </c>
+      <c r="I142">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="143" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A143">
+        <v>7</v>
+      </c>
+      <c r="B143" t="s">
+        <v>50</v>
+      </c>
+      <c r="C143">
+        <v>84</v>
+      </c>
+      <c r="D143" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E143" t="s">
+        <v>12</v>
+      </c>
+      <c r="F143" t="s">
+        <v>11</v>
+      </c>
+      <c r="G143">
+        <v>10</v>
+      </c>
+      <c r="H143">
+        <v>115</v>
+      </c>
+      <c r="I143">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="144" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A144">
+        <v>7</v>
+      </c>
+      <c r="B144" t="s">
+        <v>50</v>
+      </c>
+      <c r="C144">
+        <v>79</v>
+      </c>
+      <c r="D144" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E144" t="s">
+        <v>11</v>
+      </c>
+      <c r="F144" t="s">
+        <v>12</v>
+      </c>
+      <c r="G144">
+        <v>10</v>
+      </c>
+      <c r="H144">
+        <v>60</v>
+      </c>
+      <c r="I144">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A145">
+        <v>7</v>
+      </c>
+      <c r="B145" t="s">
+        <v>50</v>
+      </c>
+      <c r="C145">
+        <v>79</v>
+      </c>
+      <c r="D145" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E145" t="s">
+        <v>12</v>
+      </c>
+      <c r="F145" t="s">
+        <v>11</v>
+      </c>
+      <c r="G145">
+        <v>10</v>
+      </c>
+      <c r="H145">
+        <v>105</v>
+      </c>
+      <c r="I145">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A146">
+        <v>7</v>
+      </c>
+      <c r="B146" t="s">
+        <v>50</v>
+      </c>
+      <c r="C146">
+        <v>79</v>
+      </c>
+      <c r="D146" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E146" t="s">
+        <v>12</v>
+      </c>
+      <c r="F146" t="s">
+        <v>11</v>
+      </c>
+      <c r="G146">
+        <v>10</v>
+      </c>
+      <c r="H146">
+        <v>105</v>
+      </c>
+      <c r="I146">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A147">
+        <v>7</v>
+      </c>
+      <c r="B147" t="s">
+        <v>50</v>
+      </c>
+      <c r="C147">
+        <v>85</v>
+      </c>
+      <c r="D147" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E147" t="s">
+        <v>11</v>
+      </c>
+      <c r="F147" t="s">
+        <v>12</v>
+      </c>
+      <c r="G147">
+        <v>10</v>
+      </c>
+      <c r="H147">
+        <v>100</v>
+      </c>
+      <c r="I147">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A148">
+        <v>7</v>
+      </c>
+      <c r="B148" t="s">
+        <v>50</v>
+      </c>
+      <c r="C148">
+        <v>85</v>
+      </c>
+      <c r="D148" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E148" t="s">
+        <v>12</v>
+      </c>
+      <c r="F148" t="s">
+        <v>11</v>
+      </c>
+      <c r="G148">
+        <v>10</v>
+      </c>
+      <c r="H148">
+        <v>200</v>
+      </c>
+      <c r="I148">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A149">
+        <v>7</v>
+      </c>
+      <c r="B149" t="s">
+        <v>50</v>
+      </c>
+      <c r="C149">
+        <v>85</v>
+      </c>
+      <c r="D149" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E149" t="s">
+        <v>12</v>
+      </c>
+      <c r="F149" t="s">
+        <v>11</v>
+      </c>
+      <c r="G149">
+        <v>10</v>
+      </c>
+      <c r="H149">
+        <v>200</v>
+      </c>
+      <c r="I149">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A150">
+        <v>8</v>
+      </c>
+      <c r="B150" t="s">
+        <v>53</v>
+      </c>
+      <c r="C150">
+        <v>4</v>
+      </c>
+      <c r="D150" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E150" t="s">
+        <v>11</v>
+      </c>
+      <c r="F150" t="s">
+        <v>12</v>
+      </c>
+      <c r="G150">
+        <v>10</v>
+      </c>
+      <c r="H150">
+        <v>25</v>
+      </c>
+      <c r="I150">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A151">
+        <v>8</v>
+      </c>
+      <c r="B151" t="s">
+        <v>53</v>
+      </c>
+      <c r="C151">
+        <v>4</v>
+      </c>
+      <c r="D151" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E151" t="s">
+        <v>11</v>
+      </c>
+      <c r="F151" t="s">
+        <v>12</v>
+      </c>
+      <c r="G151">
+        <v>6</v>
+      </c>
+      <c r="H151">
+        <v>40</v>
+      </c>
+      <c r="I151">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A152">
+        <v>8</v>
+      </c>
+      <c r="B152" t="s">
+        <v>53</v>
+      </c>
+      <c r="C152">
+        <v>4</v>
+      </c>
+      <c r="D152" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E152" t="s">
+        <v>12</v>
+      </c>
+      <c r="F152" t="s">
+        <v>11</v>
+      </c>
+      <c r="G152">
+        <v>10</v>
+      </c>
+      <c r="H152">
+        <v>50</v>
+      </c>
+      <c r="I152">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="153" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A153">
+        <v>8</v>
+      </c>
+      <c r="B153" t="s">
+        <v>53</v>
+      </c>
+      <c r="C153">
+        <v>4</v>
+      </c>
+      <c r="D153" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E153" t="s">
+        <v>12</v>
+      </c>
+      <c r="F153" t="s">
+        <v>11</v>
+      </c>
+      <c r="G153">
+        <v>10</v>
+      </c>
+      <c r="H153">
+        <v>50</v>
+      </c>
+      <c r="I153">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A154">
+        <v>8</v>
+      </c>
+      <c r="B154" t="s">
+        <v>53</v>
+      </c>
+      <c r="C154">
+        <v>11</v>
+      </c>
+      <c r="D154" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E154" t="s">
+        <v>11</v>
+      </c>
+      <c r="F154" t="s">
+        <v>12</v>
+      </c>
+      <c r="G154">
+        <v>10</v>
+      </c>
+      <c r="H154">
+        <v>70</v>
+      </c>
+      <c r="I154">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A155">
+        <v>8</v>
+      </c>
+      <c r="B155" t="s">
+        <v>53</v>
+      </c>
+      <c r="C155">
+        <v>11</v>
+      </c>
+      <c r="D155" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E155" t="s">
+        <v>12</v>
+      </c>
+      <c r="F155" t="s">
+        <v>11</v>
+      </c>
+      <c r="G155">
+        <v>10</v>
+      </c>
+      <c r="H155">
+        <v>130</v>
+      </c>
+      <c r="I155">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A156">
+        <v>8</v>
+      </c>
+      <c r="B156" t="s">
+        <v>53</v>
+      </c>
+      <c r="C156">
+        <v>11</v>
+      </c>
+      <c r="D156" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E156" t="s">
+        <v>12</v>
+      </c>
+      <c r="F156" t="s">
+        <v>11</v>
+      </c>
+      <c r="G156">
+        <v>10</v>
+      </c>
+      <c r="H156">
+        <v>130</v>
+      </c>
+      <c r="I156">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A157">
+        <v>8</v>
+      </c>
+      <c r="B157" t="s">
+        <v>53</v>
+      </c>
+      <c r="C157">
+        <v>101</v>
+      </c>
+      <c r="D157" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E157" t="s">
+        <v>11</v>
+      </c>
+      <c r="F157" t="s">
+        <v>12</v>
+      </c>
+      <c r="G157">
+        <v>10</v>
+      </c>
+      <c r="H157">
+        <v>40</v>
+      </c>
+      <c r="I157">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A158">
+        <v>8</v>
+      </c>
+      <c r="B158" t="s">
+        <v>53</v>
+      </c>
+      <c r="C158">
+        <v>101</v>
+      </c>
+      <c r="D158" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E158" t="s">
+        <v>12</v>
+      </c>
+      <c r="F158" t="s">
+        <v>11</v>
+      </c>
+      <c r="G158">
+        <v>10</v>
+      </c>
+      <c r="H158">
+        <v>80</v>
+      </c>
+      <c r="I158">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A159">
+        <v>8</v>
+      </c>
+      <c r="B159" t="s">
+        <v>53</v>
+      </c>
+      <c r="C159">
+        <v>57</v>
+      </c>
+      <c r="D159" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E159" t="s">
+        <v>11</v>
+      </c>
+      <c r="F159" t="s">
+        <v>12</v>
+      </c>
+      <c r="G159">
+        <v>10</v>
+      </c>
+      <c r="H159">
+        <v>40</v>
+      </c>
+      <c r="I159">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A160">
+        <v>8</v>
+      </c>
+      <c r="B160" t="s">
+        <v>53</v>
+      </c>
+      <c r="C160">
+        <v>57</v>
+      </c>
+      <c r="D160" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E160" t="s">
+        <v>11</v>
+      </c>
+      <c r="F160" t="s">
+        <v>12</v>
+      </c>
+      <c r="G160">
+        <v>6</v>
+      </c>
+      <c r="H160">
+        <v>60</v>
+      </c>
+      <c r="I160">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A161">
+        <v>8</v>
+      </c>
+      <c r="B161" t="s">
+        <v>53</v>
+      </c>
+      <c r="C161">
+        <v>57</v>
+      </c>
+      <c r="D161" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E161" t="s">
+        <v>12</v>
+      </c>
+      <c r="F161" t="s">
+        <v>11</v>
+      </c>
+      <c r="G161">
+        <v>8</v>
+      </c>
+      <c r="H161">
+        <v>80</v>
+      </c>
+      <c r="I161">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A162">
+        <v>8</v>
+      </c>
+      <c r="B162" t="s">
+        <v>53</v>
+      </c>
+      <c r="C162">
+        <v>57</v>
+      </c>
+      <c r="D162" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E162" t="s">
+        <v>12</v>
+      </c>
+      <c r="F162" t="s">
+        <v>11</v>
+      </c>
+      <c r="G162">
+        <v>8</v>
+      </c>
+      <c r="H162">
+        <v>80</v>
+      </c>
+      <c r="I162">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A163">
+        <v>8</v>
+      </c>
+      <c r="B163" t="s">
+        <v>53</v>
+      </c>
+      <c r="C163">
+        <v>89</v>
+      </c>
+      <c r="D163" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E163" t="s">
+        <v>11</v>
+      </c>
+      <c r="F163" t="s">
+        <v>12</v>
+      </c>
+      <c r="G163">
+        <v>10</v>
+      </c>
+      <c r="H163">
+        <v>7.5</v>
+      </c>
+      <c r="I163">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A164">
+        <v>8</v>
+      </c>
+      <c r="B164" t="s">
+        <v>53</v>
+      </c>
+      <c r="C164">
+        <v>89</v>
+      </c>
+      <c r="D164" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E164" t="s">
+        <v>12</v>
+      </c>
+      <c r="F164" t="s">
+        <v>11</v>
+      </c>
+      <c r="G164">
+        <v>10</v>
+      </c>
+      <c r="H164">
+        <v>12.5</v>
+      </c>
+      <c r="I164">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A165">
+        <v>8</v>
+      </c>
+      <c r="B165" t="s">
+        <v>53</v>
+      </c>
+      <c r="C165">
+        <v>89</v>
+      </c>
+      <c r="D165" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E165" t="s">
+        <v>12</v>
+      </c>
+      <c r="F165" t="s">
+        <v>11</v>
+      </c>
+      <c r="G165">
+        <v>10</v>
+      </c>
+      <c r="H165">
+        <v>12.5</v>
+      </c>
+      <c r="I165">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A166">
+        <v>8</v>
+      </c>
+      <c r="B166" t="s">
+        <v>53</v>
+      </c>
+      <c r="C166">
+        <v>33</v>
+      </c>
+      <c r="D166" t="s">
+        <v>56</v>
+      </c>
+      <c r="E166" t="s">
+        <v>11</v>
+      </c>
+      <c r="F166" t="s">
+        <v>12</v>
+      </c>
+      <c r="G166">
+        <v>10</v>
+      </c>
+      <c r="H166">
+        <v>20</v>
+      </c>
+      <c r="I166">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A167">
+        <v>8</v>
+      </c>
+      <c r="B167" t="s">
+        <v>53</v>
+      </c>
+      <c r="C167">
+        <v>33</v>
+      </c>
+      <c r="D167" t="s">
+        <v>56</v>
+      </c>
+      <c r="E167" t="s">
+        <v>12</v>
+      </c>
+      <c r="F167" t="s">
+        <v>11</v>
+      </c>
+      <c r="G167">
+        <v>10</v>
+      </c>
+      <c r="H167">
+        <v>52</v>
+      </c>
+      <c r="I167">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="168" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A168">
+        <v>8</v>
+      </c>
+      <c r="B168" t="s">
+        <v>53</v>
+      </c>
+      <c r="C168">
+        <v>1</v>
+      </c>
+      <c r="D168" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E168" t="s">
+        <v>11</v>
+      </c>
+      <c r="F168" t="s">
+        <v>12</v>
+      </c>
+      <c r="G168">
+        <v>10</v>
+      </c>
+      <c r="H168">
+        <v>25</v>
+      </c>
+      <c r="I168">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A169">
+        <v>8</v>
+      </c>
+      <c r="B169" t="s">
+        <v>53</v>
+      </c>
+      <c r="C169">
+        <v>1</v>
+      </c>
+      <c r="D169" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E169" t="s">
+        <v>12</v>
+      </c>
+      <c r="F169" t="s">
+        <v>11</v>
+      </c>
+      <c r="G169">
+        <v>10</v>
+      </c>
+      <c r="H169">
+        <v>43</v>
+      </c>
+      <c r="I169">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A170">
+        <v>8</v>
+      </c>
+      <c r="B170" t="s">
+        <v>53</v>
+      </c>
+      <c r="C170">
+        <v>1</v>
+      </c>
+      <c r="D170" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E170" t="s">
+        <v>12</v>
+      </c>
+      <c r="F170" t="s">
+        <v>11</v>
+      </c>
+      <c r="G170">
+        <v>10</v>
+      </c>
+      <c r="H170">
+        <v>43</v>
+      </c>
+      <c r="I170">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A171">
+        <v>9</v>
+      </c>
+      <c r="B171" t="s">
+        <v>57</v>
+      </c>
+      <c r="C171">
+        <v>84</v>
+      </c>
+      <c r="D171" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E171" t="s">
+        <v>11</v>
+      </c>
+      <c r="F171" t="s">
+        <v>12</v>
+      </c>
+      <c r="G171">
+        <v>10</v>
+      </c>
+      <c r="H171">
+        <v>75</v>
+      </c>
+      <c r="I171">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A172">
+        <v>9</v>
+      </c>
+      <c r="B172" t="s">
+        <v>57</v>
+      </c>
+      <c r="C172">
+        <v>84</v>
+      </c>
+      <c r="D172" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E172" t="s">
+        <v>12</v>
+      </c>
+      <c r="F172" t="s">
+        <v>11</v>
+      </c>
+      <c r="G172">
+        <v>10</v>
+      </c>
+      <c r="H172">
+        <v>115</v>
+      </c>
+      <c r="I172">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="173" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A173">
+        <v>9</v>
+      </c>
+      <c r="B173" t="s">
+        <v>57</v>
+      </c>
+      <c r="C173">
+        <v>84</v>
+      </c>
+      <c r="D173" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E173" t="s">
+        <v>12</v>
+      </c>
+      <c r="F173" t="s">
+        <v>11</v>
+      </c>
+      <c r="G173">
+        <v>10</v>
+      </c>
+      <c r="H173">
+        <v>115</v>
+      </c>
+      <c r="I173">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="174" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A174">
+        <v>9</v>
+      </c>
+      <c r="B174" t="s">
+        <v>57</v>
+      </c>
+      <c r="C174">
+        <v>20</v>
+      </c>
+      <c r="D174" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E174" t="s">
+        <v>11</v>
+      </c>
+      <c r="F174" t="s">
+        <v>12</v>
+      </c>
+      <c r="G174">
+        <v>10</v>
+      </c>
+      <c r="H174">
+        <v>40</v>
+      </c>
+      <c r="I174">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A175">
+        <v>9</v>
+      </c>
+      <c r="B175" t="s">
+        <v>57</v>
+      </c>
+      <c r="C175">
+        <v>20</v>
+      </c>
+      <c r="D175" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E175" t="s">
+        <v>11</v>
+      </c>
+      <c r="F175" t="s">
+        <v>12</v>
+      </c>
+      <c r="G175">
+        <v>8</v>
+      </c>
+      <c r="H175">
+        <v>60</v>
+      </c>
+      <c r="I175">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A176">
+        <v>9</v>
+      </c>
+      <c r="B176" t="s">
+        <v>57</v>
+      </c>
+      <c r="C176">
+        <v>20</v>
+      </c>
+      <c r="D176" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E176" t="s">
+        <v>12</v>
+      </c>
+      <c r="F176" t="s">
+        <v>11</v>
+      </c>
+      <c r="G176">
+        <v>10</v>
+      </c>
+      <c r="H176">
+        <v>80</v>
+      </c>
+      <c r="I176">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="177" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A177">
+        <v>9</v>
+      </c>
+      <c r="B177" t="s">
+        <v>57</v>
+      </c>
+      <c r="C177">
+        <v>20</v>
+      </c>
+      <c r="D177" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E177" t="s">
+        <v>12</v>
+      </c>
+      <c r="F177" t="s">
+        <v>11</v>
+      </c>
+      <c r="G177">
+        <v>10</v>
+      </c>
+      <c r="H177">
+        <v>80</v>
+      </c>
+      <c r="I177">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A178">
+        <v>9</v>
+      </c>
+      <c r="B178" t="s">
+        <v>57</v>
+      </c>
+      <c r="C178">
+        <v>64</v>
+      </c>
+      <c r="D178" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E178" t="s">
+        <v>11</v>
+      </c>
+      <c r="F178" t="s">
+        <v>12</v>
+      </c>
+      <c r="G178">
+        <v>10</v>
+      </c>
+      <c r="H178">
+        <v>80</v>
+      </c>
+      <c r="I178">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A179">
+        <v>9</v>
+      </c>
+      <c r="B179" t="s">
+        <v>57</v>
+      </c>
+      <c r="C179">
+        <v>64</v>
+      </c>
+      <c r="D179" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E179" t="s">
+        <v>12</v>
+      </c>
+      <c r="F179" t="s">
+        <v>11</v>
+      </c>
+      <c r="G179">
+        <v>10</v>
+      </c>
+      <c r="H179">
+        <v>120</v>
+      </c>
+      <c r="I179">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A180">
+        <v>9</v>
+      </c>
+      <c r="B180" t="s">
+        <v>57</v>
+      </c>
+      <c r="C180">
+        <v>64</v>
+      </c>
+      <c r="D180" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E180" t="s">
+        <v>12</v>
+      </c>
+      <c r="F180" t="s">
+        <v>11</v>
+      </c>
+      <c r="G180">
+        <v>10</v>
+      </c>
+      <c r="H180">
+        <v>120</v>
+      </c>
+      <c r="I180">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A181">
+        <v>9</v>
+      </c>
+      <c r="B181" t="s">
+        <v>57</v>
+      </c>
+      <c r="C181">
+        <v>77</v>
+      </c>
+      <c r="D181" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E181" t="s">
+        <v>11</v>
+      </c>
+      <c r="F181" t="s">
+        <v>12</v>
+      </c>
+      <c r="G181">
+        <v>10</v>
+      </c>
+      <c r="H181">
+        <v>150</v>
+      </c>
+      <c r="I181">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="182" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A182">
+        <v>9</v>
+      </c>
+      <c r="B182" t="s">
+        <v>57</v>
+      </c>
+      <c r="C182">
+        <v>77</v>
+      </c>
+      <c r="D182" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E182" t="s">
+        <v>12</v>
+      </c>
+      <c r="F182" t="s">
+        <v>11</v>
+      </c>
+      <c r="G182">
+        <v>10</v>
+      </c>
+      <c r="H182">
+        <v>300</v>
+      </c>
+      <c r="I182">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A183">
+        <v>9</v>
+      </c>
+      <c r="B183" t="s">
+        <v>57</v>
+      </c>
+      <c r="C183">
+        <v>88</v>
+      </c>
+      <c r="D183" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E183" t="s">
+        <v>11</v>
+      </c>
+      <c r="F183" t="s">
+        <v>12</v>
+      </c>
+      <c r="G183">
+        <v>10</v>
+      </c>
+      <c r="H183">
+        <v>150</v>
+      </c>
+      <c r="I183">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A184">
+        <v>9</v>
+      </c>
+      <c r="B184" t="s">
+        <v>57</v>
+      </c>
+      <c r="C184">
+        <v>88</v>
+      </c>
+      <c r="D184" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E184" t="s">
+        <v>12</v>
+      </c>
+      <c r="F184" t="s">
+        <v>11</v>
+      </c>
+      <c r="G184">
+        <v>10</v>
+      </c>
+      <c r="H184">
+        <v>270</v>
+      </c>
+      <c r="I184">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="185" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A185">
+        <v>9</v>
+      </c>
+      <c r="B185" t="s">
+        <v>57</v>
+      </c>
+      <c r="C185">
+        <v>88</v>
+      </c>
+      <c r="D185" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E185" t="s">
+        <v>12</v>
+      </c>
+      <c r="F185" t="s">
+        <v>11</v>
+      </c>
+      <c r="G185">
+        <v>10</v>
+      </c>
+      <c r="H185">
+        <v>270</v>
+      </c>
+      <c r="I185">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="186" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A186">
+        <v>10</v>
+      </c>
+      <c r="B186" t="s">
+        <v>59</v>
+      </c>
+      <c r="C186">
+        <v>35</v>
+      </c>
+      <c r="D186" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E186" t="s">
+        <v>11</v>
+      </c>
+      <c r="F186" t="s">
+        <v>12</v>
+      </c>
+      <c r="G186">
+        <v>10</v>
+      </c>
+      <c r="H186">
+        <v>10</v>
+      </c>
+      <c r="I186">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="187" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A187">
+        <v>10</v>
+      </c>
+      <c r="B187" t="s">
+        <v>59</v>
+      </c>
+      <c r="C187">
+        <v>35</v>
+      </c>
+      <c r="D187" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E187" t="s">
+        <v>12</v>
+      </c>
+      <c r="F187" t="s">
+        <v>11</v>
+      </c>
+      <c r="G187">
+        <v>10</v>
+      </c>
+      <c r="H187">
+        <v>20</v>
+      </c>
+      <c r="I187">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="188" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A188">
+        <v>10</v>
+      </c>
+      <c r="B188" t="s">
+        <v>59</v>
+      </c>
+      <c r="C188">
+        <v>35</v>
+      </c>
+      <c r="D188" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E188" t="s">
+        <v>12</v>
+      </c>
+      <c r="F188" t="s">
+        <v>11</v>
+      </c>
+      <c r="G188">
+        <v>10</v>
+      </c>
+      <c r="H188">
+        <v>20</v>
+      </c>
+      <c r="I188">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="189" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A189">
+        <v>10</v>
+      </c>
+      <c r="B189" t="s">
+        <v>59</v>
+      </c>
+      <c r="C189">
+        <v>108</v>
+      </c>
+      <c r="D189" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E189" t="s">
+        <v>11</v>
+      </c>
+      <c r="F189" t="s">
+        <v>12</v>
+      </c>
+      <c r="G189">
+        <v>10</v>
+      </c>
+      <c r="H189">
+        <v>20</v>
+      </c>
+      <c r="I189">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="190" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A190">
+        <v>10</v>
+      </c>
+      <c r="B190" t="s">
+        <v>59</v>
+      </c>
+      <c r="C190">
+        <v>108</v>
+      </c>
+      <c r="D190" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E190" t="s">
+        <v>12</v>
+      </c>
+      <c r="F190" t="s">
+        <v>11</v>
+      </c>
+      <c r="G190">
+        <v>10</v>
+      </c>
+      <c r="H190">
+        <v>30</v>
+      </c>
+      <c r="I190">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A191">
+        <v>10</v>
+      </c>
+      <c r="B191" t="s">
+        <v>59</v>
+      </c>
+      <c r="C191">
+        <v>108</v>
+      </c>
+      <c r="D191" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E191" t="s">
+        <v>12</v>
+      </c>
+      <c r="F191" t="s">
+        <v>11</v>
+      </c>
+      <c r="G191">
+        <v>10</v>
+      </c>
+      <c r="H191">
+        <v>30</v>
+      </c>
+      <c r="I191">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="192" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A192">
+        <v>10</v>
+      </c>
+      <c r="B192" t="s">
+        <v>59</v>
+      </c>
+      <c r="C192">
+        <v>40</v>
+      </c>
+      <c r="D192" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E192" t="s">
+        <v>12</v>
+      </c>
+      <c r="F192" t="s">
+        <v>11</v>
+      </c>
+      <c r="G192">
+        <v>10</v>
+      </c>
+      <c r="H192">
+        <v>16</v>
+      </c>
+      <c r="I192">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A193">
+        <v>10</v>
+      </c>
+      <c r="B193" t="s">
+        <v>59</v>
+      </c>
+      <c r="C193">
+        <v>105</v>
+      </c>
+      <c r="D193" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E193" t="s">
+        <v>11</v>
+      </c>
+      <c r="F193" t="s">
+        <v>12</v>
+      </c>
+      <c r="G193">
+        <v>10</v>
+      </c>
+      <c r="H193">
+        <v>5</v>
+      </c>
+      <c r="I193">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="194" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A194">
+        <v>10</v>
+      </c>
+      <c r="B194" t="s">
+        <v>59</v>
+      </c>
+      <c r="C194">
+        <v>105</v>
+      </c>
+      <c r="D194" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E194" t="s">
+        <v>12</v>
+      </c>
+      <c r="F194" t="s">
+        <v>11</v>
+      </c>
+      <c r="G194">
+        <v>10</v>
+      </c>
+      <c r="H194">
+        <v>12.5</v>
+      </c>
+      <c r="I194">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="195" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A195">
+        <v>10</v>
+      </c>
+      <c r="B195" t="s">
+        <v>59</v>
+      </c>
+      <c r="C195">
+        <v>37</v>
+      </c>
+      <c r="D195" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E195" t="s">
+        <v>12</v>
+      </c>
+      <c r="F195" t="s">
+        <v>11</v>
+      </c>
+      <c r="G195">
+        <v>10</v>
+      </c>
+      <c r="H195">
+        <v>16</v>
+      </c>
+      <c r="I195">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="196" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A196">
+        <v>10</v>
+      </c>
+      <c r="B196" t="s">
+        <v>59</v>
+      </c>
+      <c r="C196">
+        <v>96</v>
+      </c>
+      <c r="D196" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E196" t="s">
+        <v>11</v>
+      </c>
+      <c r="F196" t="s">
+        <v>12</v>
+      </c>
+      <c r="G196">
+        <v>10</v>
+      </c>
+      <c r="H196">
+        <v>25</v>
+      </c>
+      <c r="I196">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="197" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A197">
+        <v>10</v>
+      </c>
+      <c r="B197" t="s">
+        <v>59</v>
+      </c>
+      <c r="C197">
+        <v>96</v>
+      </c>
+      <c r="D197" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E197" t="s">
+        <v>12</v>
+      </c>
+      <c r="F197" t="s">
+        <v>11</v>
+      </c>
+      <c r="G197">
+        <v>10</v>
+      </c>
+      <c r="H197">
+        <v>50</v>
+      </c>
+      <c r="I197">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
